--- a/ct/tests/fixtures/repository_cutover/workspace/excel/ItemType.xlsx
+++ b/ct/tests/fixtures/repository_cutover/workspace/excel/ItemType.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Code
+          <t>CodeName
 string</t>
         </is>
       </c>
